--- a/output/mrio_table_styled.xlsx
+++ b/output/mrio_table_styled.xlsx
@@ -1,167 +1,171 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/parvulesco/Documents/R/LEEDS_MODEL/output/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1D312F-B2B2-3244-BA0B-F31177C06E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MRIO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MRIO" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
-  <si>
-    <t xml:space="preserve">Intermediate Demand (ID)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Demand (FD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aggregate Demand (D)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RoW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industry Demand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Investment</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">HH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gov†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Industry Output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z₁₁
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
+  <si>
+    <t>Intermediate Demand (ID)</t>
+  </si>
+  <si>
+    <t>Final Demand (FD)</t>
+  </si>
+  <si>
+    <t>Aggregate Demand (D)</t>
+  </si>
+  <si>
+    <t>EU</t>
+  </si>
+  <si>
+    <t>RoW</t>
+  </si>
+  <si>
+    <t>Consumption</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Industry Output</t>
+  </si>
+  <si>
+    <t>Z₁₁
 EU → EU</t>
   </si>
   <si>
-    <t xml:space="preserve">Z₁₂
+    <t>Z₁₂
 EU → RoW</t>
   </si>
   <si>
-    <t xml:space="preserve">β₁c₁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">σ₁g₁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ι₁·id₁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ιᵍ₁·idᵍ₁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d₁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z₂₁
+    <t>β₁c₁</t>
+  </si>
+  <si>
+    <t>σ₁g₁</t>
+  </si>
+  <si>
+    <t>ι₁·id₁</t>
+  </si>
+  <si>
+    <t>ιᵍ₁·idᵍ₁</t>
+  </si>
+  <si>
+    <t>d₁</t>
+  </si>
+  <si>
+    <t>Z₂₁
 RoW → EU</t>
   </si>
   <si>
-    <t xml:space="preserve">Z₂₂
+    <t>Z₂₂
 RoW → RoW</t>
   </si>
   <si>
-    <t xml:space="preserve">β₂c₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">σ₂g₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ι₂·id₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ιᵍ₂·idᵍ₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value Added</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W — wages → households</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W₁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P — profits → capitalists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P₁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T — taxes → government</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T₁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Value Added</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VA₁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VA₂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aggregate Supply</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d₁ᵀ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d₂ᵀ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note. Rows = selling/producing region; columns = buying region (ID) or consuming institution (FD). Subscript on share vectors (β, σ, ι): supplying region r. Subscript on aggregates (c, g, id): consuming region s. Green cells: domestic flow (r = s). Pink cells: cross-border flow (r ≠ s). W (wages) → households; P (profits) → capitalists; T (taxes) → government. † Public investment idᵍᵣ is an optimal-control stabilizer.</t>
+    <t>β₂c₂</t>
+  </si>
+  <si>
+    <t>σ₂g₂</t>
+  </si>
+  <si>
+    <t>ι₂·id₂</t>
+  </si>
+  <si>
+    <t>ιᵍ₂·idᵍ₂</t>
+  </si>
+  <si>
+    <t>d₂</t>
+  </si>
+  <si>
+    <t>Value Added</t>
+  </si>
+  <si>
+    <t>W₁</t>
+  </si>
+  <si>
+    <t>W₂</t>
+  </si>
+  <si>
+    <t>P₁</t>
+  </si>
+  <si>
+    <t>P₂</t>
+  </si>
+  <si>
+    <t>T₁</t>
+  </si>
+  <si>
+    <t>T₂</t>
+  </si>
+  <si>
+    <t>Total Value Added</t>
+  </si>
+  <si>
+    <t>VA₁</t>
+  </si>
+  <si>
+    <t>VA₂</t>
+  </si>
+  <si>
+    <t>Aggregate Supply</t>
+  </si>
+  <si>
+    <t>d₁ᵀ</t>
+  </si>
+  <si>
+    <t>d₂ᵀ</t>
+  </si>
+  <si>
+    <t>Note. Rows = selling/producing region; columns = buying region (ID) or consuming institution (FD). Subscript on share vectors (β, σ, ι): supplying region r. Subscript on aggregates (c, g, id): consuming region s. Green cells: domestic flow (r = s). Pink cells: cross-border flow (r ≠ s). W (wages) → households; P (profits) → capitalists; T (taxes) → government. † Public investment idᵍᵣ is an optimal-control stabilizer.</t>
+  </si>
+  <si>
+    <t>Firm Circulating Investment</t>
+  </si>
+  <si>
+    <t>households</t>
+  </si>
+  <si>
+    <t>government</t>
+  </si>
+  <si>
+    <t>firm fixed</t>
+  </si>
+  <si>
+    <t>wages</t>
+  </si>
+  <si>
+    <t>profits</t>
+  </si>
+  <si>
+    <t>taxes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -170,42 +174,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
-      <b/>
+      <family val="1"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF1B2A3B"/>
       <name val="Times New Roman"/>
-      <b/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <b/>
+      <family val="1"/>
     </font>
     <font>
+      <i/>
       <sz val="9"/>
       <color rgb="FF444444"/>
       <name val="Times New Roman"/>
-      <i/>
+      <family val="1"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
-      <b/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -234,21 +244,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0F4F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EFCF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAD7D7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFEF9E7"/>
       </patternFill>
     </fill>
@@ -257,8 +252,32 @@
         <fgColor rgb="FF1B2A3B"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -267,9 +286,13 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color rgb="FF1B2A3B"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -284,25 +307,227 @@
       <bottom style="thin">
         <color rgb="FFAAAAAA"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF1B2A3B"/>
       </top>
       <bottom style="medium">
         <color rgb="FF1B2A3B"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF1B2A3B"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1B2A3B"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1B2A3B"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF1B2A3B"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -313,38 +538,132 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -626,327 +945,329 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="24.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="13.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="13.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="13.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="13.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="13.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="13.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="6.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" customWidth="1"/>
+    <col min="5" max="12" width="8.83203125" customWidth="1"/>
+    <col min="13" max="13" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="12"/>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12" t="s">
+    <row r="1" spans="1:13" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12" t="s">
+      <c r="D1" s="7"/>
+      <c r="E1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12" t="s">
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
+    <row r="2" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+    <row r="3" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="9"/>
+      <c r="G3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
+      <c r="H3" s="9"/>
+      <c r="I3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" s="2"/>
+      <c r="L3" s="9"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:13" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="B5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="D5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="E5" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="3" t="s">
+      <c r="F5" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="3" t="s">
+      <c r="J5" s="32" t="s">
         <v>13</v>
       </c>
+      <c r="K5" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" s="20" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="7" t="s">
+    <row r="6" spans="1:13" ht="34" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="D6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="E6" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="F6" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="8" t="s">
+      <c r="G6" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="J6" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="9" t="s">
+      <c r="K6" s="29" t="s">
         <v>21</v>
       </c>
+      <c r="L6" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="18" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="8" t="s">
+    <row r="7" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="B7" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="D7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="8" t="s">
+    </row>
+    <row r="8" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="9" t="s">
+      <c r="D8" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="4" t="s">
+    <row r="9" spans="1:13" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="D9" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="10" t="s">
+    </row>
+    <row r="10" spans="1:13" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="B10" s="11"/>
+      <c r="C10" s="16" t="s">
         <v>32</v>
       </c>
+      <c r="D10" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
     </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="10" t="s">
+    <row r="11" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="B11" s="11"/>
+      <c r="C11" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="D11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="10" t="s">
+    <row r="12" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="11" t="s">
-        <v>45</v>
-      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:L1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="I2:L2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:M12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>